--- a/Mapping.xlsx
+++ b/Mapping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nadia\Desktop\Python\Final_Project_Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46DE6DC2-1D0B-4A36-99F7-D0C768C07A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21BC301F-3CA7-43B8-B20D-183C08BF55CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="300" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="130">
   <si>
     <t>description</t>
   </si>
@@ -157,12 +157,6 @@
     <t>quantity</t>
   </si>
   <si>
-    <t>measure_unit</t>
-  </si>
-  <si>
-    <t>unit measurement</t>
-  </si>
-  <si>
     <t>total_price</t>
   </si>
   <si>
@@ -419,6 +413,9 @@
   </si>
   <si>
     <t>Transactions table</t>
+  </si>
+  <si>
+    <t>GetTransactions.transaction type</t>
   </si>
 </sst>
 </file>
@@ -580,7 +577,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -626,12 +623,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -639,7 +630,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -921,7 +917,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G755"/>
+  <dimension ref="A1:G754"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="43.5546875" customWidth="1"/>
@@ -937,25 +933,25 @@
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="10"/>
-      <c r="D1" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="E1" s="18"/>
-      <c r="F1" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="G1" s="18"/>
+      <c r="D1" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="21"/>
+      <c r="F1" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1" s="21"/>
     </row>
     <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="21" t="s">
-        <v>126</v>
-      </c>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
+      <c r="C2" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
@@ -983,7 +979,7 @@
         <v>4</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
@@ -1000,11 +996,11 @@
         <v>11</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="12" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G5" s="1"/>
     </row>
@@ -1019,11 +1015,11 @@
         <v>12</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="12" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G6" s="1"/>
     </row>
@@ -1038,11 +1034,11 @@
         <v>0</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="15" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G7" s="1"/>
     </row>
@@ -1057,11 +1053,11 @@
         <v>15</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="15" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G8" s="1"/>
     </row>
@@ -1076,11 +1072,11 @@
         <v>18</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="12" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G9" s="1"/>
     </row>
@@ -1098,8 +1094,8 @@
         <v>19</v>
       </c>
       <c r="B11" s="1"/>
-      <c r="C11" s="20" t="s">
-        <v>127</v>
+      <c r="C11" s="18" t="s">
+        <v>125</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -1132,11 +1128,11 @@
         <v>4</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="12" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G13" s="1"/>
     </row>
@@ -1151,11 +1147,11 @@
         <v>22</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="12" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G14" s="1"/>
     </row>
@@ -1170,11 +1166,11 @@
         <v>24</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G15" s="1"/>
     </row>
@@ -1189,13 +1185,13 @@
         <v>26</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G16" s="1"/>
     </row>
@@ -1210,11 +1206,11 @@
         <v>28</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="12" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G17" s="1"/>
     </row>
@@ -1229,14 +1225,14 @@
         <v>15</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E18" s="12"/>
       <c r="F18" s="12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="115.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1250,10 +1246,10 @@
         <v>31</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1267,10 +1263,10 @@
         <v>31</v>
       </c>
       <c r="D20" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="E20" s="12" t="s">
         <v>73</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>75</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
@@ -1298,11 +1294,11 @@
         <v>33</v>
       </c>
       <c r="B23" s="1"/>
-      <c r="C23" s="20" t="s">
-        <v>128</v>
+      <c r="C23" s="18" t="s">
+        <v>126</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
@@ -1349,14 +1345,14 @@
         <v>34</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E26" s="1"/>
       <c r="F26" s="16" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1380,8 +1376,8 @@
         <v>35</v>
       </c>
       <c r="B29" s="3"/>
-      <c r="C29" s="20" t="s">
-        <v>129</v>
+      <c r="C29" s="18" t="s">
+        <v>127</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
@@ -1414,13 +1410,13 @@
         <v>37</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G31" s="1"/>
     </row>
@@ -1435,10 +1431,10 @@
         <v>39</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
@@ -1454,11 +1450,11 @@
         <v>41</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E33" s="1"/>
       <c r="F33" s="12" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G33" s="1"/>
     </row>
@@ -1473,15 +1469,15 @@
         <v>42</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E34" s="1"/>
       <c r="F34" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G34" s="1"/>
     </row>
-    <row r="35" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>43</v>
       </c>
@@ -1491,75 +1487,69 @@
       <c r="C35" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="D35" s="1"/>
+      <c r="D35" s="12" t="s">
+        <v>82</v>
+      </c>
       <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
+      <c r="F35" s="12" t="s">
+        <v>114</v>
+      </c>
       <c r="G35" s="1"/>
     </row>
-    <row r="36" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="1" t="s">
+    <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C36" s="11" t="s">
+      <c r="B36" s="1"/>
+      <c r="C36" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D36" s="12" t="s">
-        <v>84</v>
+      <c r="D36" s="14" t="s">
+        <v>74</v>
       </c>
       <c r="E36" s="1"/>
-      <c r="F36" s="12" t="s">
-        <v>116</v>
+      <c r="F36" s="14" t="s">
+        <v>74</v>
       </c>
       <c r="G36" s="1"/>
     </row>
     <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="9" t="s">
-        <v>47</v>
+      <c r="A37" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="B37" s="1"/>
-      <c r="C37" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D37" s="14" t="s">
-        <v>76</v>
-      </c>
+      <c r="C37" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D37" s="1"/>
       <c r="E37" s="1"/>
-      <c r="F37" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="G37" s="1"/>
-    </row>
-    <row r="38" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F37" s="1"/>
+      <c r="G37" s="16"/>
+    </row>
+    <row r="38" spans="1:7" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="D38" s="1"/>
+        <v>47</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>83</v>
+      </c>
       <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="16"/>
-    </row>
-    <row r="39" spans="1:7" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="1" t="s">
-        <v>5</v>
-      </c>
+      <c r="F38" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="G38" s="1"/>
+    </row>
+    <row r="39" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="1"/>
       <c r="B39" s="1"/>
-      <c r="C39" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>85</v>
-      </c>
+      <c r="C39" s="11"/>
+      <c r="D39" s="1"/>
       <c r="E39" s="1"/>
-      <c r="F39" s="12" t="s">
-        <v>117</v>
-      </c>
+      <c r="F39" s="1"/>
       <c r="G39" s="1"/>
     </row>
     <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1572,21 +1562,25 @@
       <c r="G40" s="1"/>
     </row>
     <row r="41" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="1"/>
+      <c r="A41" s="9" t="s">
+        <v>48</v>
+      </c>
       <c r="B41" s="1"/>
-      <c r="C41" s="11"/>
+      <c r="C41" s="18" t="s">
+        <v>128</v>
+      </c>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
     </row>
     <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="9" t="s">
-        <v>50</v>
+      <c r="A42" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="B42" s="1"/>
-      <c r="C42" s="20" t="s">
-        <v>130</v>
+      <c r="C42" s="11" t="s">
+        <v>2</v>
       </c>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
@@ -1595,69 +1589,75 @@
     </row>
     <row r="43" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B43" s="1"/>
       <c r="C43" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="D43" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>84</v>
+      </c>
       <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
+      <c r="F43" s="12" t="s">
+        <v>116</v>
+      </c>
       <c r="G43" s="1"/>
     </row>
-    <row r="44" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="B44" s="1"/>
       <c r="C44" s="11" t="s">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="E44" s="1"/>
-      <c r="F44" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E44" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="F44" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="G44" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="G44" s="1"/>
-    </row>
-    <row r="45" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="45" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>51</v>
       </c>
       <c r="B45" s="1"/>
       <c r="C45" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D45" t="s">
+        <v>86</v>
+      </c>
+      <c r="E45" s="1"/>
+      <c r="F45" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G45" s="1"/>
+    </row>
+    <row r="46" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D45" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="E45" s="12" t="s">
+      <c r="B46" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D46" s="12" t="s">
         <v>87</v>
-      </c>
-      <c r="F45" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B46" s="1"/>
-      <c r="C46" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D46" s="22" t="s">
-        <v>88</v>
       </c>
       <c r="E46" s="1"/>
       <c r="F46" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G46" s="1"/>
     </row>
@@ -1665,18 +1665,16 @@
       <c r="A47" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>17</v>
-      </c>
+      <c r="B47" s="1"/>
       <c r="C47" s="11" t="s">
         <v>55</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E47" s="1"/>
       <c r="F47" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G47" s="1"/>
     </row>
@@ -1684,35 +1682,29 @@
       <c r="A48" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B48" s="1"/>
-      <c r="C48" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="D48" s="12" t="s">
-        <v>90</v>
+      <c r="B48" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C48" s="4"/>
+      <c r="D48" s="1" t="s">
+        <v>129</v>
       </c>
       <c r="E48" s="1"/>
       <c r="F48" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="G48" s="1"/>
+        <v>122</v>
+      </c>
+      <c r="G48" s="16"/>
     </row>
     <row r="49" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>17</v>
-      </c>
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
       <c r="C49" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
-      <c r="F49" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="G49" s="16"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
     </row>
     <row r="50" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="1"/>
@@ -8033,11 +8025,6 @@
       <c r="G751" s="1"/>
     </row>
     <row r="752" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A752" s="1"/>
-      <c r="B752" s="1"/>
-      <c r="C752" s="11"/>
-      <c r="D752" s="1"/>
-      <c r="E752" s="1"/>
       <c r="F752" s="1"/>
       <c r="G752" s="1"/>
     </row>
@@ -8048,10 +8035,6 @@
     <row r="754" spans="6:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F754" s="1"/>
       <c r="G754" s="1"/>
-    </row>
-    <row r="755" spans="6:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="F755" s="1"/>
-      <c r="G755" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8063,10 +8046,10 @@
     <hyperlink ref="D13" r:id="rId2" display="http://getorders.orders.id/" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="D31" r:id="rId3" display="http://ecomorders.id/" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
     <hyperlink ref="D32" r:id="rId4" display="http://ecomitems.id/" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="D44" r:id="rId5" display="http://gettransactions.transactions.id/" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="D45" r:id="rId6" display="http://ecomorders.id/" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="D43" r:id="rId5" display="http://gettransactions.transactions.id/" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="D44" r:id="rId6" display="http://ecomorders.id/" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
     <hyperlink ref="F31" r:id="rId7" display="http://ecomorders.id/" xr:uid="{A5E2ABEB-8D16-41F3-85DB-FC91F83E6BD3}"/>
-    <hyperlink ref="F45" r:id="rId8" display="http://ecomorder.id/" xr:uid="{1F4C2370-9D75-4296-885F-B376AF7D6B65}"/>
+    <hyperlink ref="F44" r:id="rId8" display="http://ecomorder.id/" xr:uid="{1F4C2370-9D75-4296-885F-B376AF7D6B65}"/>
     <hyperlink ref="G26" r:id="rId9" xr:uid="{8B3A4F5E-1B71-485F-B488-FC1EB929A729}"/>
     <hyperlink ref="F26" r:id="rId10" xr:uid="{56BF8EB5-9F13-45D9-AF4F-0B7CDB190280}"/>
     <hyperlink ref="D20" r:id="rId11" display="http://ecomorderstatuses.id/" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
@@ -8084,42 +8067,42 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
